--- a/wishlist_maia-clara.xlsx
+++ b/wishlist_maia-clara.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cfn7021\Downloads\wishlist\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a5351de14e4a67c9/Downloads/wishlist/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA0B68F1-5427-485F-9E19-42B7065C6256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="43" documentId="13_ncr:1_{EA0B68F1-5427-485F-9E19-42B7065C6256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7EA81D33-B6EA-4324-8111-6317C98333E3}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="29010" windowHeight="23280" xr2:uid="{FE4DC328-739C-48AF-B2EF-9BDF321350CE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FE4DC328-739C-48AF-B2EF-9BDF321350CE}"/>
   </bookViews>
   <sheets>
     <sheet name="Wishlist Maia &amp; Clara" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="284">
   <si>
     <t>Image</t>
   </si>
@@ -835,6 +835,63 @@
   </si>
   <si>
     <t>SKIP</t>
+  </si>
+  <si>
+    <t>https://www.seilpark-zuerich.ch/temp/compressed_logo_jubilaeum.png</t>
+  </si>
+  <si>
+    <t>https://shop.e-guma.ch/seilpark-zuerich/en/gift-vouchers/47195/voucher-entry-ticket</t>
+  </si>
+  <si>
+    <t>Voucher ZOO ZH</t>
+  </si>
+  <si>
+    <t>https://www.zoo.ch/en/onlineshop/geschenkkarten/gift-card</t>
+  </si>
+  <si>
+    <t>https://zoo-live.rokka.io/product_cropped_xs_1x/57ed224f1e21c761861be8eca1bdc1303224e9fe/geschenkkarte-2019-zoozuerich-01.png?itok=dUiUOVfF</t>
+  </si>
+  <si>
+    <t>https://www.zalando.ch/geschenk-gutscheine/</t>
+  </si>
+  <si>
+    <t>Voucher Zalando</t>
+  </si>
+  <si>
+    <t>https://img01.ztat.net/article/spp-media-p1/47411619894742e0a3e7e3279001927d/53ad875805b34f7b8a81d3df7cea5f16.jpg?imwidth=300</t>
+  </si>
+  <si>
+    <t>Voucher Seilpark  - Mini 4-5 years</t>
+  </si>
+  <si>
+    <t>Voucher Fliplab</t>
+  </si>
+  <si>
+    <t>https://fliplab.ch/zurich/wp-content/uploads/2023/09/fliplab-logo-icon.svg</t>
+  </si>
+  <si>
+    <t>https://fliplab.ch/zurich/tickets-preise/</t>
+  </si>
+  <si>
+    <t>Backpack Seal</t>
+  </si>
+  <si>
+    <t>https://www.affenzahn.com/en/backpack-large-friend-seal-2023</t>
+  </si>
+  <si>
+    <t>https://fondof.getbynder.com/transform/064f5c74-3ca3-4115-86bd-eb577e406692/01438-30203-10-Affenzahn-Groer-Freund-Robbe_product_01?io=transform:extend,width:800,height:800</t>
+  </si>
+  <si>
+    <t>4 CHF</t>
+  </si>
+  <si>
+    <t>19 CHF</t>
+  </si>
+  <si>
+    <t>60 EUR</t>
+  </si>
+  <si>
+    <t>Haine masura 104</t>
   </si>
 </sst>
 </file>
@@ -913,6 +970,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1213,7 +1274,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CF9E297-72DE-4386-8002-570237626454}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:E93"/>
+  <dimension ref="A1:E100"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="26.140625" customWidth="1"/>
@@ -1609,6 +1670,9 @@
       <c r="D23" t="s">
         <v>125</v>
       </c>
+      <c r="E23" t="s">
+        <v>264</v>
+      </c>
     </row>
     <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
@@ -2467,11 +2531,14 @@
       <c r="B74" t="s">
         <v>119</v>
       </c>
-      <c r="C74" t="s">
+      <c r="C74" s="1" t="s">
         <v>105</v>
       </c>
       <c r="D74" t="s">
         <v>106</v>
+      </c>
+      <c r="E74" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="75" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
@@ -2631,6 +2698,9 @@
       <c r="C84" t="s">
         <v>204</v>
       </c>
+      <c r="E84" t="s">
+        <v>264</v>
+      </c>
     </row>
     <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
@@ -2780,6 +2850,89 @@
       </c>
       <c r="D93" t="s">
         <v>137</v>
+      </c>
+      <c r="E93" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>277</v>
+      </c>
+      <c r="B94" t="s">
+        <v>279</v>
+      </c>
+      <c r="C94" t="s">
+        <v>278</v>
+      </c>
+      <c r="D94" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>273</v>
+      </c>
+      <c r="B95" t="s">
+        <v>265</v>
+      </c>
+      <c r="C95" t="s">
+        <v>266</v>
+      </c>
+      <c r="D95" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>267</v>
+      </c>
+      <c r="B96" t="s">
+        <v>269</v>
+      </c>
+      <c r="C96" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>271</v>
+      </c>
+      <c r="B97" t="s">
+        <v>272</v>
+      </c>
+      <c r="C97" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>274</v>
+      </c>
+      <c r="B99" t="s">
+        <v>275</v>
+      </c>
+      <c r="C99" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>104</v>
+      </c>
+      <c r="B100" t="s">
+        <v>119</v>
+      </c>
+      <c r="C100" t="s">
+        <v>105</v>
+      </c>
+      <c r="D100" t="s">
+        <v>280</v>
       </c>
     </row>
   </sheetData>
@@ -2838,9 +2991,10 @@
     <hyperlink ref="C41" r:id="rId41" xr:uid="{3896E971-69EB-42D0-9AFB-82F67A2DA246}"/>
     <hyperlink ref="C44" r:id="rId42" xr:uid="{A23C3A5D-032E-41A1-8364-30E60FD75B38}"/>
     <hyperlink ref="B62" r:id="rId43" xr:uid="{5AF2D273-A962-485D-85DB-E4B8AD7BB70D}"/>
+    <hyperlink ref="C74" r:id="rId44" xr:uid="{8F80D271-ACC1-4671-83B3-E4512CD27919}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId44"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId45"/>
 </worksheet>
 </file>
 

--- a/wishlist_maia-clara.xlsx
+++ b/wishlist_maia-clara.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a5351de14e4a67c9/Downloads/wishlist/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="43" documentId="13_ncr:1_{EA0B68F1-5427-485F-9E19-42B7065C6256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7EA81D33-B6EA-4324-8111-6317C98333E3}"/>
+  <xr:revisionPtr revIDLastSave="44" documentId="13_ncr:1_{EA0B68F1-5427-485F-9E19-42B7065C6256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16DDD1D7-910C-42F8-B3EC-454F795FC4AB}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FE4DC328-739C-48AF-B2EF-9BDF321350CE}"/>
   </bookViews>
   <sheets>
-    <sheet name="Wishlist Maia &amp; Clara" sheetId="1" r:id="rId1"/>
+    <sheet name="Wishlist Maia" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Wishlist Maia &amp; Clara'!$A$1:$E$93</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Wishlist Maia'!$A$1:$E$93</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>

--- a/wishlist_maia-clara.xlsx
+++ b/wishlist_maia-clara.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a5351de14e4a67c9/Downloads/wishlist/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="44" documentId="13_ncr:1_{EA0B68F1-5427-485F-9E19-42B7065C6256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16DDD1D7-910C-42F8-B3EC-454F795FC4AB}"/>
+  <xr:revisionPtr revIDLastSave="45" documentId="13_ncr:1_{EA0B68F1-5427-485F-9E19-42B7065C6256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{857797C3-E56F-4025-B048-96495E816898}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FE4DC328-739C-48AF-B2EF-9BDF321350CE}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="284">
   <si>
     <t>Image</t>
   </si>
@@ -970,10 +970,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2868,6 +2864,9 @@
       <c r="D94" t="s">
         <v>282</v>
       </c>
+      <c r="E94" t="s">
+        <v>264</v>
+      </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
